--- a/data/移动应用开发/达成/模板样例/10-课程达成度评价图表.xlsx
+++ b/data/移动应用开发/达成/模板样例/10-课程达成度评价图表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2025-2026\2025-2026-2\期末\移动应用开发\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FlutterProjects\knowledge_graph_app\data\移动应用开发\达成\模板样例\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EDF87A-9E93-445F-95F0-AE7A30BAC398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CBFEB2-EDDA-4AF4-9CE2-C846EF80A421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="807" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="807" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="期末成绩" sheetId="11" r:id="rId1"/>
@@ -99,16 +99,7 @@
     <t>学号</t>
   </si>
   <si>
-    <t>满分10</t>
-  </si>
-  <si>
-    <t>满分20</t>
-  </si>
-  <si>
     <t>满分30</t>
-  </si>
-  <si>
-    <t>满分40</t>
   </si>
   <si>
     <t>项目（30%）</t>
@@ -158,32 +149,6 @@
   </si>
   <si>
     <r>
-      <t>满分1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>满分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 20</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>满分</t>
     </r>
     <r>
@@ -193,42 +158,6 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve"> 30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>满分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>40</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>实验1得分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（满分5分）</t>
     </r>
   </si>
   <si>
@@ -252,52 +181,6 @@
         <charset val="134"/>
       </rPr>
       <t>（满分5分）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>实验3得分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（满分10分）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>实验4得分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（满分10分）</t>
     </r>
   </si>
   <si>
@@ -344,29 +227,6 @@
         <charset val="134"/>
       </rPr>
       <t>（满分15分）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>实验7得分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（满分40分）</t>
     </r>
   </si>
   <si>
@@ -1182,6 +1042,156 @@
   <si>
     <t>课程总体目标达成度(cc)</t>
   </si>
+  <si>
+    <t>满分15</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>满分25</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>满分30</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>满分1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>满分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 25</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>满分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>实验1得分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（满分15分）</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>实验4得分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（满分10分）</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>实验3得分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（满分15分）</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>实验7得分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（满分30分）</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1500,7 +1510,7 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1651,27 +1661,19 @@
     <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="10" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="24" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="24" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1680,12 +1682,17 @@
     <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="10" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1695,19 +1702,34 @@
     <xf numFmtId="176" fontId="16" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="10" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="24" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="24" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="24" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="15" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1731,6 +1753,12 @@
     <xf numFmtId="179" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="10" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1749,23 +1777,11 @@
     <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="13" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -12897,8 +12913,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="604092"/>
-          <a:ext cx="1960736" cy="918470"/>
+          <a:off x="0" y="592831"/>
+          <a:ext cx="1964114" cy="919596"/>
           <a:chOff x="-61" y="76"/>
           <a:chExt cx="354" cy="89"/>
         </a:xfrm>
@@ -13461,7 +13477,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="94" y="74"/>
-          <a:ext cx="955198" cy="893962"/>
+          <a:ext cx="954448" cy="878947"/>
           <a:chOff x="94" y="74"/>
           <a:chExt cx="1214344" cy="876226"/>
         </a:xfrm>
@@ -15963,134 +15979,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="68"/>
+      <c r="A1" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="39" customHeight="1">
-      <c r="A2" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="74" t="s">
+      <c r="A2" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
       <c r="K2" s="20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.2">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="75">
+      <c r="B3" s="73"/>
+      <c r="C3" s="74">
         <v>1</v>
       </c>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75">
+      <c r="D3" s="74"/>
+      <c r="E3" s="74">
         <v>2</v>
       </c>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76" t="s">
+      <c r="F3" s="74"/>
+      <c r="G3" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75">
+      <c r="H3" s="74"/>
+      <c r="I3" s="74">
         <v>4</v>
       </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="67" t="s">
+      <c r="J3" s="76"/>
+      <c r="K3" s="80" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="69" t="s">
+      <c r="B4" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="92" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" s="81" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="92" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="69" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="69" t="s">
+      <c r="G4" s="81" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="81" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="92" t="s">
+        <v>272</v>
+      </c>
+      <c r="J4" s="82"/>
+      <c r="K4" s="69"/>
+    </row>
+    <row r="5" spans="1:11" ht="44.1" customHeight="1">
+      <c r="A5" s="73"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="D5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="E5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="G5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="70"/>
-      <c r="K4" s="68"/>
-    </row>
-    <row r="5" spans="1:11" ht="44.1" customHeight="1">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="I5" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="J5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="20" t="s">
         <v>12</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="16.2">
       <c r="A6" s="25" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C6" s="53">
         <v>90</v>
@@ -16122,10 +16138,10 @@
     </row>
     <row r="7" spans="1:11" ht="16.2">
       <c r="A7" s="25" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C7" s="53">
         <v>90</v>
@@ -16157,10 +16173,10 @@
     </row>
     <row r="8" spans="1:11" ht="16.2">
       <c r="A8" s="25" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C8" s="53">
         <v>86</v>
@@ -16192,10 +16208,10 @@
     </row>
     <row r="9" spans="1:11" ht="16.2">
       <c r="A9" s="25" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C9" s="53">
         <v>86</v>
@@ -16227,10 +16243,10 @@
     </row>
     <row r="10" spans="1:11" ht="16.2">
       <c r="A10" s="25" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C10" s="53">
         <v>86</v>
@@ -16262,10 +16278,10 @@
     </row>
     <row r="11" spans="1:11" ht="16.2">
       <c r="A11" s="25" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C11" s="53">
         <v>80</v>
@@ -16297,10 +16313,10 @@
     </row>
     <row r="12" spans="1:11" ht="16.2">
       <c r="A12" s="25" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C12" s="53">
         <v>82</v>
@@ -16332,10 +16348,10 @@
     </row>
     <row r="13" spans="1:11" ht="16.2">
       <c r="A13" s="25" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C13" s="53">
         <v>90</v>
@@ -16367,10 +16383,10 @@
     </row>
     <row r="14" spans="1:11" ht="16.2">
       <c r="A14" s="25" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C14" s="53">
         <v>78</v>
@@ -16402,10 +16418,10 @@
     </row>
     <row r="15" spans="1:11" ht="16.2">
       <c r="A15" s="25" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C15" s="53">
         <v>94</v>
@@ -16437,10 +16453,10 @@
     </row>
     <row r="16" spans="1:11" ht="16.2">
       <c r="A16" s="25" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C16" s="53">
         <v>88</v>
@@ -16472,10 +16488,10 @@
     </row>
     <row r="17" spans="1:11" ht="16.2">
       <c r="A17" s="25" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C17" s="53">
         <v>100</v>
@@ -16507,10 +16523,10 @@
     </row>
     <row r="18" spans="1:11" ht="16.2">
       <c r="A18" s="25" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C18" s="53">
         <v>80</v>
@@ -16542,10 +16558,10 @@
     </row>
     <row r="19" spans="1:11" ht="16.2">
       <c r="A19" s="25" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C19" s="53">
         <v>80</v>
@@ -16577,10 +16593,10 @@
     </row>
     <row r="20" spans="1:11" ht="16.2">
       <c r="A20" s="25" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C20" s="53">
         <v>82</v>
@@ -16612,10 +16628,10 @@
     </row>
     <row r="21" spans="1:11" ht="16.2">
       <c r="A21" s="25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C21" s="53">
         <v>80</v>
@@ -16647,10 +16663,10 @@
     </row>
     <row r="22" spans="1:11" ht="16.2">
       <c r="A22" s="25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C22" s="53">
         <v>74</v>
@@ -16682,10 +16698,10 @@
     </row>
     <row r="23" spans="1:11" ht="16.2">
       <c r="A23" s="25" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C23" s="53">
         <v>86</v>
@@ -16717,10 +16733,10 @@
     </row>
     <row r="24" spans="1:11" ht="16.2">
       <c r="A24" s="25" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C24" s="53">
         <v>76</v>
@@ -16752,10 +16768,10 @@
     </row>
     <row r="25" spans="1:11" ht="16.2">
       <c r="A25" s="25" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C25" s="53">
         <v>88</v>
@@ -16787,10 +16803,10 @@
     </row>
     <row r="26" spans="1:11" ht="16.2">
       <c r="A26" s="25" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C26" s="53">
         <v>68</v>
@@ -16822,10 +16838,10 @@
     </row>
     <row r="27" spans="1:11" ht="16.2">
       <c r="A27" s="25" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C27" s="53">
         <v>80</v>
@@ -16857,10 +16873,10 @@
     </row>
     <row r="28" spans="1:11" ht="16.2">
       <c r="A28" s="25" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C28" s="53">
         <v>90</v>
@@ -16892,10 +16908,10 @@
     </row>
     <row r="29" spans="1:11" ht="16.2">
       <c r="A29" s="25" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C29" s="53">
         <v>64</v>
@@ -16927,10 +16943,10 @@
     </row>
     <row r="30" spans="1:11" ht="16.2">
       <c r="A30" s="25" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C30" s="53">
         <v>94</v>
@@ -16962,10 +16978,10 @@
     </row>
     <row r="31" spans="1:11" ht="16.2">
       <c r="A31" s="25" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C31" s="53">
         <v>80</v>
@@ -16997,10 +17013,10 @@
     </row>
     <row r="32" spans="1:11" ht="16.2">
       <c r="A32" s="25" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C32" s="53">
         <v>90</v>
@@ -17032,10 +17048,10 @@
     </row>
     <row r="33" spans="1:11" ht="16.2">
       <c r="A33" s="25" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C33" s="53">
         <v>72</v>
@@ -17067,10 +17083,10 @@
     </row>
     <row r="34" spans="1:11" ht="16.2">
       <c r="A34" s="25" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C34" s="53">
         <v>76</v>
@@ -17102,10 +17118,10 @@
     </row>
     <row r="35" spans="1:11" ht="16.2">
       <c r="A35" s="25" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C35" s="53">
         <v>98</v>
@@ -17137,10 +17153,10 @@
     </row>
     <row r="36" spans="1:11" ht="16.2">
       <c r="A36" s="25" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C36" s="53">
         <v>96</v>
@@ -17172,10 +17188,10 @@
     </row>
     <row r="37" spans="1:11" ht="16.2">
       <c r="A37" s="25" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C37" s="53">
         <v>89</v>
@@ -17207,10 +17223,10 @@
     </row>
     <row r="38" spans="1:11" ht="16.2">
       <c r="A38" s="25" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C38" s="53">
         <v>80</v>
@@ -17242,10 +17258,10 @@
     </row>
     <row r="39" spans="1:11" ht="16.2">
       <c r="A39" s="25" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C39" s="53">
         <v>80</v>
@@ -17277,10 +17293,10 @@
     </row>
     <row r="40" spans="1:11" ht="16.2">
       <c r="A40" s="25" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C40" s="53">
         <v>96</v>
@@ -17312,10 +17328,10 @@
     </row>
     <row r="41" spans="1:11" ht="16.2">
       <c r="A41" s="25" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C41" s="53">
         <v>78</v>
@@ -17347,10 +17363,10 @@
     </row>
     <row r="42" spans="1:11" ht="16.2">
       <c r="A42" s="25" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C42" s="53">
         <v>90</v>
@@ -17382,10 +17398,10 @@
     </row>
     <row r="43" spans="1:11" ht="16.2">
       <c r="A43" s="25" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C43" s="53">
         <v>93</v>
@@ -17417,10 +17433,10 @@
     </row>
     <row r="44" spans="1:11" ht="16.2">
       <c r="A44" s="25" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C44" s="53">
         <v>74</v>
@@ -17452,10 +17468,10 @@
     </row>
     <row r="45" spans="1:11" ht="16.2">
       <c r="A45" s="25" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C45" s="53">
         <v>80</v>
@@ -17487,10 +17503,10 @@
     </row>
     <row r="46" spans="1:11" ht="16.2">
       <c r="A46" s="25" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C46" s="53">
         <v>92</v>
@@ -17522,10 +17538,10 @@
     </row>
     <row r="47" spans="1:11" ht="16.2">
       <c r="A47" s="25" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C47" s="53">
         <v>80</v>
@@ -17557,10 +17573,10 @@
     </row>
     <row r="48" spans="1:11" ht="16.2">
       <c r="A48" s="25" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C48" s="53">
         <v>72</v>
@@ -17592,10 +17608,10 @@
     </row>
     <row r="49" spans="1:11" ht="16.2">
       <c r="A49" s="25" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C49" s="53">
         <v>80</v>
@@ -17627,10 +17643,10 @@
     </row>
     <row r="50" spans="1:11" ht="16.2">
       <c r="A50" s="25" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C50" s="53">
         <v>86</v>
@@ -17662,10 +17678,10 @@
     </row>
     <row r="51" spans="1:11" ht="16.2">
       <c r="A51" s="25" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C51" s="53">
         <v>96</v>
@@ -17697,10 +17713,10 @@
     </row>
     <row r="52" spans="1:11" ht="16.2">
       <c r="A52" s="25" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C52" s="53">
         <v>78</v>
@@ -17732,10 +17748,10 @@
     </row>
     <row r="53" spans="1:11" ht="16.2">
       <c r="A53" s="25" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C53" s="53">
         <v>76</v>
@@ -17767,10 +17783,10 @@
     </row>
     <row r="54" spans="1:11" ht="16.2">
       <c r="A54" s="25" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C54" s="53">
         <v>92</v>
@@ -17802,10 +17818,10 @@
     </row>
     <row r="55" spans="1:11" ht="16.2">
       <c r="A55" s="25" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C55" s="53">
         <v>78</v>
@@ -17837,10 +17853,10 @@
     </row>
     <row r="56" spans="1:11" ht="16.2">
       <c r="A56" s="25" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C56" s="53">
         <v>88</v>
@@ -17872,10 +17888,10 @@
     </row>
     <row r="57" spans="1:11" ht="16.2">
       <c r="A57" s="25" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C57" s="53">
         <v>70</v>
@@ -17907,10 +17923,10 @@
     </row>
     <row r="58" spans="1:11" ht="16.2">
       <c r="A58" s="25" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C58" s="53">
         <v>62</v>
@@ -17942,10 +17958,10 @@
     </row>
     <row r="59" spans="1:11" ht="16.2">
       <c r="A59" s="25" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C59" s="53">
         <v>76</v>
@@ -17977,10 +17993,10 @@
     </row>
     <row r="60" spans="1:11" ht="16.2">
       <c r="A60" s="25" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C60" s="53">
         <v>76</v>
@@ -18012,10 +18028,10 @@
     </row>
     <row r="61" spans="1:11" ht="16.2">
       <c r="A61" s="25" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C61" s="53">
         <v>96</v>
@@ -18047,10 +18063,10 @@
     </row>
     <row r="62" spans="1:11" ht="16.2">
       <c r="A62" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C62" s="53">
         <v>100</v>
@@ -18082,10 +18098,10 @@
     </row>
     <row r="63" spans="1:11" ht="16.2">
       <c r="A63" s="25" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C63" s="53">
         <v>66</v>
@@ -18117,10 +18133,10 @@
     </row>
     <row r="64" spans="1:11" ht="16.2">
       <c r="A64" s="25" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C64" s="53">
         <v>94</v>
@@ -18152,10 +18168,10 @@
     </row>
     <row r="65" spans="1:11" ht="16.2">
       <c r="A65" s="25" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C65" s="53">
         <v>80</v>
@@ -18187,10 +18203,10 @@
     </row>
     <row r="66" spans="1:11" ht="16.2">
       <c r="A66" s="25" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C66" s="53">
         <v>96</v>
@@ -18222,10 +18238,10 @@
     </row>
     <row r="67" spans="1:11" ht="16.2">
       <c r="A67" s="25" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C67" s="53">
         <v>88</v>
@@ -18257,10 +18273,10 @@
     </row>
     <row r="68" spans="1:11" ht="16.2">
       <c r="A68" s="25" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C68" s="53">
         <v>92</v>
@@ -18292,10 +18308,10 @@
     </row>
     <row r="69" spans="1:11" ht="16.2">
       <c r="A69" s="25" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C69" s="53">
         <v>90</v>
@@ -18327,10 +18343,10 @@
     </row>
     <row r="70" spans="1:11" ht="16.2">
       <c r="A70" s="25" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C70" s="53">
         <v>90</v>
@@ -18362,10 +18378,10 @@
     </row>
     <row r="71" spans="1:11" ht="16.2">
       <c r="A71" s="25" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C71" s="53">
         <v>92</v>
@@ -18397,10 +18413,10 @@
     </row>
     <row r="72" spans="1:11" ht="16.2">
       <c r="A72" s="25" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C72" s="53">
         <v>90</v>
@@ -18432,10 +18448,10 @@
     </row>
     <row r="73" spans="1:11" ht="16.2">
       <c r="A73" s="25" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C73" s="53">
         <v>90</v>
@@ -18467,10 +18483,10 @@
     </row>
     <row r="74" spans="1:11" ht="16.2">
       <c r="A74" s="25" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C74" s="53">
         <v>100</v>
@@ -18502,10 +18518,10 @@
     </row>
     <row r="75" spans="1:11" ht="16.2">
       <c r="A75" s="25" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C75" s="53">
         <v>92</v>
@@ -18537,10 +18553,10 @@
     </row>
     <row r="76" spans="1:11" ht="16.2">
       <c r="A76" s="25" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C76" s="53">
         <v>100</v>
@@ -18572,10 +18588,10 @@
     </row>
     <row r="77" spans="1:11" ht="16.2">
       <c r="A77" s="25" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C77" s="53">
         <v>70</v>
@@ -18607,10 +18623,10 @@
     </row>
     <row r="78" spans="1:11" ht="16.2">
       <c r="A78" s="25" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C78" s="53">
         <v>94</v>
@@ -18642,10 +18658,10 @@
     </row>
     <row r="79" spans="1:11" ht="16.2">
       <c r="A79" s="25" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C79" s="53">
         <v>80</v>
@@ -18677,10 +18693,10 @@
     </row>
     <row r="80" spans="1:11" ht="16.2">
       <c r="A80" s="25" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C80" s="53">
         <v>80</v>
@@ -18712,10 +18728,10 @@
     </row>
     <row r="81" spans="1:11" ht="16.2">
       <c r="A81" s="25" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C81" s="53">
         <v>80</v>
@@ -18747,10 +18763,10 @@
     </row>
     <row r="82" spans="1:11" ht="16.2">
       <c r="A82" s="25" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C82" s="53">
         <v>78</v>
@@ -18782,10 +18798,10 @@
     </row>
     <row r="83" spans="1:11" ht="16.2">
       <c r="A83" s="25" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C83" s="53">
         <v>90</v>
@@ -18817,10 +18833,10 @@
     </row>
     <row r="84" spans="1:11" ht="16.2">
       <c r="A84" s="25" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C84" s="53">
         <v>96</v>
@@ -18852,10 +18868,10 @@
     </row>
     <row r="85" spans="1:11" ht="16.2">
       <c r="A85" s="25" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C85" s="53">
         <v>92</v>
@@ -18887,10 +18903,10 @@
     </row>
     <row r="86" spans="1:11" ht="16.2">
       <c r="A86" s="25" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C86" s="53">
         <v>84</v>
@@ -18922,10 +18938,10 @@
     </row>
     <row r="87" spans="1:11" ht="16.2">
       <c r="A87" s="25" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C87" s="53">
         <v>90</v>
@@ -18957,10 +18973,10 @@
     </row>
     <row r="88" spans="1:11" ht="16.2">
       <c r="A88" s="25" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C88" s="53">
         <v>86</v>
@@ -18992,10 +19008,10 @@
     </row>
     <row r="89" spans="1:11" ht="16.2">
       <c r="A89" s="25" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C89" s="53">
         <v>86</v>
@@ -19027,10 +19043,10 @@
     </row>
     <row r="90" spans="1:11" ht="16.2">
       <c r="A90" s="25" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C90" s="53">
         <v>100</v>
@@ -19061,10 +19077,10 @@
       </c>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="B91" s="63"/>
+      <c r="A91" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="B91" s="78"/>
       <c r="C91" s="56">
         <v>85</v>
       </c>
@@ -19094,10 +19110,10 @@
       </c>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="B92" s="63"/>
+      <c r="A92" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="78"/>
       <c r="C92" s="59"/>
       <c r="D92" s="54">
         <v>0.85040000000000004</v>
@@ -19120,14 +19136,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
@@ -19137,6 +19145,14 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
@@ -20370,147 +20386,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="71" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
     </row>
     <row r="2" spans="1:14" ht="16.2">
-      <c r="A2" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="65" t="s">
-        <v>269</v>
-      </c>
-      <c r="C2" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
+      <c r="A2" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="73" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
       <c r="N2" s="20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.2">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="75">
+      <c r="B3" s="73"/>
+      <c r="C3" s="74">
         <v>1</v>
       </c>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75">
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74">
         <v>2</v>
       </c>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="79">
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="83">
         <v>3</v>
       </c>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79">
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83">
         <v>4</v>
       </c>
-      <c r="M3" s="79"/>
-      <c r="N3" s="67" t="s">
+      <c r="M3" s="83"/>
+      <c r="N3" s="80" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="69" t="s">
+      <c r="B4" s="79"/>
+      <c r="C4" s="92" t="s">
+        <v>273</v>
+      </c>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="103" t="s">
+        <v>275</v>
+      </c>
+      <c r="M4" s="86"/>
+      <c r="N4" s="69"/>
+    </row>
+    <row r="5" spans="1:14" ht="47.4">
+      <c r="A5" s="73"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="81"/>
-      <c r="N4" s="68"/>
-    </row>
-    <row r="5" spans="1:14" ht="47.4">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>28</v>
-      </c>
       <c r="K5" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="21" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="62" t="s">
+        <v>279</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="25" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C6" s="19">
         <v>100</v>
@@ -20549,10 +20565,10 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="25" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C7" s="19">
         <v>65</v>
@@ -20591,10 +20607,10 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="25" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C8" s="19">
         <v>75</v>
@@ -20633,10 +20649,10 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="25" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C9" s="19">
         <v>85</v>
@@ -20675,10 +20691,10 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="25" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C10" s="19">
         <v>85</v>
@@ -20717,10 +20733,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="25" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C11" s="19">
         <v>70</v>
@@ -20759,10 +20775,10 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="25" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C12" s="19">
         <v>90</v>
@@ -20801,10 +20817,10 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="25" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C13" s="19">
         <v>85</v>
@@ -20843,10 +20859,10 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="25" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C14" s="19">
         <v>80</v>
@@ -20885,10 +20901,10 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="25" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C15" s="19">
         <v>85</v>
@@ -20927,10 +20943,10 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="25" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C16" s="19">
         <v>75</v>
@@ -20969,10 +20985,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="25" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C17" s="19">
         <v>95</v>
@@ -21011,10 +21027,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="25" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C18" s="19">
         <v>75</v>
@@ -21053,10 +21069,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="25" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C19" s="19">
         <v>65</v>
@@ -21095,10 +21111,10 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="25" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C20" s="19">
         <v>90</v>
@@ -21137,10 +21153,10 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C21" s="19">
         <v>70</v>
@@ -21179,10 +21195,10 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C22" s="19">
         <v>80</v>
@@ -21221,10 +21237,10 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="25" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C23" s="19">
         <v>85</v>
@@ -21263,10 +21279,10 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="25" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C24" s="19">
         <v>75</v>
@@ -21305,10 +21321,10 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="25" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C25" s="19">
         <v>90</v>
@@ -21347,10 +21363,10 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="25" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C26" s="19">
         <v>65</v>
@@ -21389,10 +21405,10 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="25" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C27" s="19">
         <v>75</v>
@@ -21431,10 +21447,10 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="25" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C28" s="19">
         <v>65</v>
@@ -21473,10 +21489,10 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="25" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C29" s="19">
         <v>95</v>
@@ -21515,10 +21531,10 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="25" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C30" s="47">
         <v>80</v>
@@ -21557,10 +21573,10 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="25" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C31" s="47">
         <v>80</v>
@@ -21599,10 +21615,10 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="25" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C32" s="47">
         <v>90</v>
@@ -21641,10 +21657,10 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="25" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C33" s="47">
         <v>85</v>
@@ -21683,10 +21699,10 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="25" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C34" s="47">
         <v>65</v>
@@ -21725,10 +21741,10 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="25" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C35" s="47">
         <v>90</v>
@@ -21767,10 +21783,10 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="25" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C36" s="47">
         <v>85</v>
@@ -21809,10 +21825,10 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="25" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C37" s="47">
         <v>90</v>
@@ -21851,10 +21867,10 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="25" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C38" s="47">
         <v>95</v>
@@ -21893,10 +21909,10 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="25" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C39" s="47">
         <v>85</v>
@@ -21935,10 +21951,10 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="25" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C40" s="47">
         <v>85</v>
@@ -21977,10 +21993,10 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="25" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C41" s="47">
         <v>90</v>
@@ -22019,10 +22035,10 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="25" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C42" s="47">
         <v>80</v>
@@ -22061,10 +22077,10 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="25" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C43" s="47">
         <v>95</v>
@@ -22103,10 +22119,10 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="25" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C44" s="47">
         <v>80</v>
@@ -22145,10 +22161,10 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="25" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C45" s="47">
         <v>100</v>
@@ -22187,10 +22203,10 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="25" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C46" s="47">
         <v>100</v>
@@ -22229,10 +22245,10 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="25" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C47" s="47">
         <v>85</v>
@@ -22271,10 +22287,10 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="25" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C48" s="47">
         <v>75</v>
@@ -22313,10 +22329,10 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="25" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C49" s="47">
         <v>90</v>
@@ -22355,10 +22371,10 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="25" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C50" s="47">
         <v>85</v>
@@ -22397,10 +22413,10 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="25" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C51" s="47">
         <v>95</v>
@@ -22439,10 +22455,10 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="25" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C52" s="47">
         <v>95</v>
@@ -22481,10 +22497,10 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="25" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C53" s="47">
         <v>80</v>
@@ -22523,10 +22539,10 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="25" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C54" s="47">
         <v>85</v>
@@ -22565,10 +22581,10 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="25" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C55" s="47">
         <v>85</v>
@@ -22607,10 +22623,10 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="25" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C56" s="47">
         <v>85</v>
@@ -22649,10 +22665,10 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="25" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C57" s="47">
         <v>100</v>
@@ -22691,10 +22707,10 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="25" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C58" s="47">
         <v>90</v>
@@ -22733,10 +22749,10 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="25" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C59" s="47">
         <v>75</v>
@@ -22775,10 +22791,10 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="25" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C60" s="47">
         <v>100</v>
@@ -22817,10 +22833,10 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="25" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C61" s="47">
         <v>75</v>
@@ -22859,10 +22875,10 @@
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C62" s="47">
         <v>100</v>
@@ -22901,10 +22917,10 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="25" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C63" s="47">
         <v>75</v>
@@ -22943,10 +22959,10 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="25" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C64" s="47">
         <v>75</v>
@@ -22985,10 +23001,10 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="25" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C65" s="47">
         <v>70</v>
@@ -23027,10 +23043,10 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="25" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C66" s="47">
         <v>75</v>
@@ -23069,10 +23085,10 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="25" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C67" s="47">
         <v>65</v>
@@ -23111,10 +23127,10 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="25" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C68" s="47">
         <v>100</v>
@@ -23153,10 +23169,10 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="25" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C69" s="47">
         <v>85</v>
@@ -23195,10 +23211,10 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="25" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C70" s="47">
         <v>60</v>
@@ -23237,10 +23253,10 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="25" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C71" s="47">
         <v>80</v>
@@ -23279,10 +23295,10 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="25" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C72" s="47">
         <v>75</v>
@@ -23321,10 +23337,10 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="25" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C73" s="47">
         <v>90</v>
@@ -23363,10 +23379,10 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="25" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C74" s="47">
         <v>70</v>
@@ -23405,10 +23421,10 @@
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="25" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C75" s="47">
         <v>100</v>
@@ -23447,10 +23463,10 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="25" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C76" s="47">
         <v>75</v>
@@ -23489,10 +23505,10 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="25" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C77" s="47">
         <v>85</v>
@@ -23531,10 +23547,10 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="25" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C78" s="47">
         <v>80</v>
@@ -23573,10 +23589,10 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="25" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C79" s="47">
         <v>75</v>
@@ -23615,10 +23631,10 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="25" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C80" s="47">
         <v>85</v>
@@ -23657,10 +23673,10 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="25" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C81" s="47">
         <v>100</v>
@@ -23699,10 +23715,10 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="25" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C82" s="47">
         <v>90</v>
@@ -23741,10 +23757,10 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="25" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C83" s="47">
         <v>90</v>
@@ -23783,10 +23799,10 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="25" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C84" s="47">
         <v>50</v>
@@ -23825,10 +23841,10 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="25" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C85" s="47">
         <v>85</v>
@@ -23867,10 +23883,10 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="25" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C86" s="47">
         <v>90</v>
@@ -23909,10 +23925,10 @@
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="25" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C87" s="47">
         <v>80</v>
@@ -23951,10 +23967,10 @@
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="25" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C88" s="47">
         <v>100</v>
@@ -23993,10 +24009,10 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="25" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C89" s="47">
         <v>40</v>
@@ -24035,10 +24051,10 @@
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="25" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C90" s="47">
         <v>85</v>
@@ -24076,10 +24092,10 @@
       </c>
     </row>
     <row r="91" spans="1:14">
-      <c r="A91" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="B91" s="78"/>
+      <c r="A91" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="B91" s="85"/>
       <c r="C91" s="32">
         <v>82.6</v>
       </c>
@@ -24116,10 +24132,10 @@
       </c>
     </row>
     <row r="92" spans="1:14">
-      <c r="A92" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="B92" s="78"/>
+      <c r="A92" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="85"/>
       <c r="C92" s="34"/>
       <c r="D92" s="34"/>
       <c r="E92" s="34">
@@ -24154,14 +24170,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:M2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="L3:M3"/>
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
@@ -24171,6 +24179,14 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:M2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:M3"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
@@ -24230,318 +24246,318 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40">
-      <c r="A1" s="84" t="s">
-        <v>270</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
-      <c r="U1" s="86"/>
-      <c r="V1" s="86"/>
-      <c r="W1" s="86"/>
-      <c r="X1" s="86"/>
-      <c r="Y1" s="86"/>
-      <c r="Z1" s="86"/>
-      <c r="AA1" s="86"/>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="86"/>
-      <c r="AD1" s="86"/>
-      <c r="AE1" s="86"/>
-      <c r="AF1" s="86"/>
-      <c r="AG1" s="86"/>
-      <c r="AH1" s="86"/>
-      <c r="AI1" s="86"/>
-      <c r="AJ1" s="86"/>
-      <c r="AK1" s="86"/>
-      <c r="AL1" s="86"/>
-      <c r="AM1" s="86"/>
+      <c r="A1" s="88" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="90"/>
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
+      <c r="AK1" s="90"/>
+      <c r="AL1" s="90"/>
+      <c r="AM1" s="90"/>
     </row>
     <row r="2" spans="1:40">
-      <c r="A2" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
+      <c r="W2" s="83"/>
+      <c r="X2" s="83"/>
+      <c r="Y2" s="83"/>
+      <c r="Z2" s="83"/>
+      <c r="AA2" s="83"/>
+      <c r="AB2" s="83"/>
+      <c r="AC2" s="83"/>
+      <c r="AD2" s="83"/>
+      <c r="AE2" s="83"/>
+      <c r="AF2" s="83"/>
+      <c r="AG2" s="83"/>
+      <c r="AH2" s="83"/>
+      <c r="AI2" s="83"/>
+      <c r="AJ2" s="83"/>
+      <c r="AK2" s="83"/>
+      <c r="AL2" s="83"/>
+      <c r="AM2" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="91">
+        <v>1</v>
+      </c>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="80">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
+      <c r="A4" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="87"/>
+      <c r="C4" s="92" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="93" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="90"/>
+      <c r="T4" s="90"/>
+      <c r="U4" s="90"/>
+      <c r="V4" s="90"/>
+      <c r="W4" s="90"/>
+      <c r="X4" s="90"/>
+      <c r="Y4" s="90"/>
+      <c r="Z4" s="90"/>
+      <c r="AA4" s="90"/>
+      <c r="AB4" s="93" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC4" s="90"/>
+      <c r="AD4" s="90"/>
+      <c r="AE4" s="90"/>
+      <c r="AF4" s="90"/>
+      <c r="AG4" s="90"/>
+      <c r="AH4" s="90"/>
+      <c r="AI4" s="90"/>
+      <c r="AJ4" s="90"/>
+      <c r="AK4" s="90"/>
+      <c r="AL4" s="90"/>
+      <c r="AM4" s="90"/>
+    </row>
+    <row r="5" spans="1:40" ht="46.95" customHeight="1">
+      <c r="A5" s="72"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="79" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="79"/>
-      <c r="AD2" s="79"/>
-      <c r="AE2" s="79"/>
-      <c r="AF2" s="79"/>
-      <c r="AG2" s="79"/>
-      <c r="AH2" s="79"/>
-      <c r="AI2" s="79"/>
-      <c r="AJ2" s="79"/>
-      <c r="AK2" s="79"/>
-      <c r="AL2" s="79"/>
-      <c r="AM2" s="20" t="s">
+      <c r="L5" s="22" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:40">
-      <c r="A3" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="87">
-        <v>1</v>
-      </c>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="67">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67">
-        <v>4</v>
-      </c>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="67"/>
-      <c r="AG3" s="67"/>
-      <c r="AH3" s="67"/>
-      <c r="AI3" s="67"/>
-      <c r="AJ3" s="67"/>
-      <c r="AK3" s="67"/>
-      <c r="AL3" s="67"/>
-      <c r="AM3" s="67" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40">
-      <c r="A4" s="64" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="88" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86"/>
-      <c r="S4" s="86"/>
-      <c r="T4" s="86"/>
-      <c r="U4" s="86"/>
-      <c r="V4" s="86"/>
-      <c r="W4" s="86"/>
-      <c r="X4" s="86"/>
-      <c r="Y4" s="86"/>
-      <c r="Z4" s="86"/>
-      <c r="AA4" s="86"/>
-      <c r="AB4" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC4" s="86"/>
-      <c r="AD4" s="86"/>
-      <c r="AE4" s="86"/>
-      <c r="AF4" s="86"/>
-      <c r="AG4" s="86"/>
-      <c r="AH4" s="86"/>
-      <c r="AI4" s="86"/>
-      <c r="AJ4" s="86"/>
-      <c r="AK4" s="86"/>
-      <c r="AL4" s="86"/>
-      <c r="AM4" s="86"/>
-    </row>
-    <row r="5" spans="1:40" ht="46.95" customHeight="1">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="22" t="s">
+      <c r="M5" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="N5" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="O5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="P5" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="Q5" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="R5" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="S5" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="T5" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="U5" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="V5" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="W5" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="X5" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="Y5" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="23" t="s">
+      <c r="Z5" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="AA5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB5" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="R5" s="23" t="s">
+      <c r="AC5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="S5" s="23" t="s">
+      <c r="AD5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="T5" s="23" t="s">
+      <c r="AE5" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="U5" s="23" t="s">
+      <c r="AF5" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="V5" s="23" t="s">
+      <c r="AG5" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="AH5" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="AI5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="AJ5" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="Z5" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB5" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC5" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD5" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE5" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF5" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG5" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH5" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI5" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="AJ5" s="23" t="s">
-        <v>63</v>
-      </c>
       <c r="AK5" s="24" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="AL5" s="23" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AM5" s="20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:40">
       <c r="A6" s="25" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C6" s="22">
         <v>69.3</v>
@@ -24604,10 +24620,10 @@
     </row>
     <row r="7" spans="1:40">
       <c r="A7" s="25" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C7" s="22">
         <v>70.8</v>
@@ -24670,10 +24686,10 @@
     </row>
     <row r="8" spans="1:40">
       <c r="A8" s="25" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C8" s="22">
         <v>39.799999999999997</v>
@@ -24736,10 +24752,10 @@
     </row>
     <row r="9" spans="1:40">
       <c r="A9" s="25" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C9" s="22">
         <v>82</v>
@@ -24802,10 +24818,10 @@
     </row>
     <row r="10" spans="1:40">
       <c r="A10" s="25" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C10" s="22">
         <v>73.900000000000006</v>
@@ -24868,10 +24884,10 @@
     </row>
     <row r="11" spans="1:40">
       <c r="A11" s="25" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C11" s="22">
         <v>23</v>
@@ -24934,10 +24950,10 @@
     </row>
     <row r="12" spans="1:40">
       <c r="A12" s="25" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C12" s="22">
         <v>80.8</v>
@@ -25000,10 +25016,10 @@
     </row>
     <row r="13" spans="1:40">
       <c r="A13" s="25" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C13" s="22">
         <v>77.099999999999994</v>
@@ -25066,10 +25082,10 @@
     </row>
     <row r="14" spans="1:40">
       <c r="A14" s="25" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C14" s="22">
         <v>66.7</v>
@@ -25132,10 +25148,10 @@
     </row>
     <row r="15" spans="1:40">
       <c r="A15" s="25" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C15" s="22">
         <v>73.599999999999994</v>
@@ -25198,10 +25214,10 @@
     </row>
     <row r="16" spans="1:40">
       <c r="A16" s="25" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C16" s="22">
         <v>68.400000000000006</v>
@@ -25264,10 +25280,10 @@
     </row>
     <row r="17" spans="1:40">
       <c r="A17" s="25" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C17" s="22">
         <v>75.099999999999994</v>
@@ -25330,10 +25346,10 @@
     </row>
     <row r="18" spans="1:40">
       <c r="A18" s="25" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C18" s="22">
         <v>54.1</v>
@@ -25396,10 +25412,10 @@
     </row>
     <row r="19" spans="1:40">
       <c r="A19" s="25" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C19" s="22">
         <v>46.7</v>
@@ -25462,10 +25478,10 @@
     </row>
     <row r="20" spans="1:40">
       <c r="A20" s="25" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C20" s="22">
         <v>73</v>
@@ -25528,10 +25544,10 @@
     </row>
     <row r="21" spans="1:40">
       <c r="A21" s="25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C21" s="22">
         <v>57.7</v>
@@ -25594,10 +25610,10 @@
     </row>
     <row r="22" spans="1:40">
       <c r="A22" s="25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C22" s="22">
         <v>63.4</v>
@@ -25660,10 +25676,10 @@
     </row>
     <row r="23" spans="1:40">
       <c r="A23" s="25" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C23" s="22">
         <v>66.8</v>
@@ -25726,10 +25742,10 @@
     </row>
     <row r="24" spans="1:40">
       <c r="A24" s="25" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C24" s="22">
         <v>40</v>
@@ -25792,10 +25808,10 @@
     </row>
     <row r="25" spans="1:40">
       <c r="A25" s="25" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C25" s="22">
         <v>57.2</v>
@@ -25858,10 +25874,10 @@
     </row>
     <row r="26" spans="1:40">
       <c r="A26" s="25" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C26" s="22">
         <v>39.799999999999997</v>
@@ -25924,10 +25940,10 @@
     </row>
     <row r="27" spans="1:40">
       <c r="A27" s="25" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C27" s="22">
         <v>74.5</v>
@@ -25990,10 +26006,10 @@
     </row>
     <row r="28" spans="1:40">
       <c r="A28" s="25" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C28" s="22">
         <v>59.8</v>
@@ -26056,10 +26072,10 @@
     </row>
     <row r="29" spans="1:40">
       <c r="A29" s="25" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C29" s="22">
         <v>65</v>
@@ -26122,10 +26138,10 @@
     </row>
     <row r="30" spans="1:40">
       <c r="A30" s="25" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C30" s="22">
         <v>73.900000000000006</v>
@@ -26188,10 +26204,10 @@
     </row>
     <row r="31" spans="1:40">
       <c r="A31" s="25" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C31" s="22">
         <v>74.099999999999994</v>
@@ -26254,10 +26270,10 @@
     </row>
     <row r="32" spans="1:40">
       <c r="A32" s="25" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C32" s="22">
         <v>61.9</v>
@@ -26320,10 +26336,10 @@
     </row>
     <row r="33" spans="1:40">
       <c r="A33" s="25" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C33" s="22">
         <v>67</v>
@@ -26386,10 +26402,10 @@
     </row>
     <row r="34" spans="1:40">
       <c r="A34" s="25" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C34" s="22">
         <v>65.099999999999994</v>
@@ -26452,10 +26468,10 @@
     </row>
     <row r="35" spans="1:40">
       <c r="A35" s="25" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C35" s="22">
         <v>72.099999999999994</v>
@@ -26518,10 +26534,10 @@
     </row>
     <row r="36" spans="1:40">
       <c r="A36" s="25" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C36" s="22">
         <v>74.900000000000006</v>
@@ -26584,10 +26600,10 @@
     </row>
     <row r="37" spans="1:40">
       <c r="A37" s="25" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C37" s="22">
         <v>67.599999999999994</v>
@@ -26650,10 +26666,10 @@
     </row>
     <row r="38" spans="1:40">
       <c r="A38" s="25" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C38" s="22">
         <v>64.5</v>
@@ -26716,10 +26732,10 @@
     </row>
     <row r="39" spans="1:40">
       <c r="A39" s="25" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C39" s="22">
         <v>64.599999999999994</v>
@@ -26782,10 +26798,10 @@
     </row>
     <row r="40" spans="1:40">
       <c r="A40" s="25" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C40" s="22">
         <v>69.599999999999994</v>
@@ -26848,10 +26864,10 @@
     </row>
     <row r="41" spans="1:40">
       <c r="A41" s="25" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C41" s="22">
         <v>69.400000000000006</v>
@@ -26914,10 +26930,10 @@
     </row>
     <row r="42" spans="1:40">
       <c r="A42" s="25" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C42" s="22">
         <v>67.599999999999994</v>
@@ -26980,10 +26996,10 @@
     </row>
     <row r="43" spans="1:40">
       <c r="A43" s="25" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C43" s="22">
         <v>74.8</v>
@@ -27046,10 +27062,10 @@
     </row>
     <row r="44" spans="1:40">
       <c r="A44" s="25" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C44" s="22">
         <v>69.099999999999994</v>
@@ -27112,10 +27128,10 @@
     </row>
     <row r="45" spans="1:40">
       <c r="A45" s="25" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C45" s="22">
         <v>70.3</v>
@@ -27178,10 +27194,10 @@
     </row>
     <row r="46" spans="1:40">
       <c r="A46" s="25" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C46" s="22">
         <v>79.8</v>
@@ -27244,10 +27260,10 @@
     </row>
     <row r="47" spans="1:40">
       <c r="A47" s="25" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C47" s="22">
         <v>69.8</v>
@@ -27310,10 +27326,10 @@
     </row>
     <row r="48" spans="1:40">
       <c r="A48" s="25" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C48" s="22">
         <v>76.900000000000006</v>
@@ -27376,10 +27392,10 @@
     </row>
     <row r="49" spans="1:40">
       <c r="A49" s="25" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C49" s="22">
         <v>61.1</v>
@@ -27442,10 +27458,10 @@
     </row>
     <row r="50" spans="1:40">
       <c r="A50" s="25" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C50" s="22">
         <v>63.1</v>
@@ -27508,10 +27524,10 @@
     </row>
     <row r="51" spans="1:40">
       <c r="A51" s="25" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C51" s="22">
         <v>72.7</v>
@@ -27574,10 +27590,10 @@
     </row>
     <row r="52" spans="1:40">
       <c r="A52" s="25" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C52" s="22">
         <v>74.099999999999994</v>
@@ -27640,10 +27656,10 @@
     </row>
     <row r="53" spans="1:40">
       <c r="A53" s="25" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C53" s="22">
         <v>74.900000000000006</v>
@@ -27706,10 +27722,10 @@
     </row>
     <row r="54" spans="1:40">
       <c r="A54" s="25" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C54" s="22">
         <v>70.8</v>
@@ -27772,10 +27788,10 @@
     </row>
     <row r="55" spans="1:40">
       <c r="A55" s="25" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C55" s="22">
         <v>53</v>
@@ -27838,10 +27854,10 @@
     </row>
     <row r="56" spans="1:40">
       <c r="A56" s="25" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C56" s="22">
         <v>61.6</v>
@@ -27904,10 +27920,10 @@
     </row>
     <row r="57" spans="1:40">
       <c r="A57" s="25" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C57" s="22">
         <v>71</v>
@@ -27970,10 +27986,10 @@
     </row>
     <row r="58" spans="1:40">
       <c r="A58" s="25" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C58" s="22">
         <v>62.8</v>
@@ -28036,10 +28052,10 @@
     </row>
     <row r="59" spans="1:40">
       <c r="A59" s="25" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C59" s="22">
         <v>65.5</v>
@@ -28102,10 +28118,10 @@
     </row>
     <row r="60" spans="1:40">
       <c r="A60" s="25" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C60" s="22">
         <v>68.3</v>
@@ -28168,10 +28184,10 @@
     </row>
     <row r="61" spans="1:40">
       <c r="A61" s="25" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C61" s="22">
         <v>74.099999999999994</v>
@@ -28234,10 +28250,10 @@
     </row>
     <row r="62" spans="1:40">
       <c r="A62" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C62" s="22">
         <v>76.7</v>
@@ -28300,10 +28316,10 @@
     </row>
     <row r="63" spans="1:40">
       <c r="A63" s="25" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C63" s="22">
         <v>56</v>
@@ -28366,10 +28382,10 @@
     </row>
     <row r="64" spans="1:40">
       <c r="A64" s="25" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C64" s="22">
         <v>73.2</v>
@@ -28432,10 +28448,10 @@
     </row>
     <row r="65" spans="1:40">
       <c r="A65" s="25" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C65" s="22">
         <v>61.6</v>
@@ -28498,10 +28514,10 @@
     </row>
     <row r="66" spans="1:40">
       <c r="A66" s="25" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C66" s="22">
         <v>58.4</v>
@@ -28564,10 +28580,10 @@
     </row>
     <row r="67" spans="1:40">
       <c r="A67" s="25" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C67" s="22">
         <v>65.099999999999994</v>
@@ -28630,10 +28646,10 @@
     </row>
     <row r="68" spans="1:40">
       <c r="A68" s="25" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C68" s="22">
         <v>78.3</v>
@@ -28696,10 +28712,10 @@
     </row>
     <row r="69" spans="1:40">
       <c r="A69" s="25" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C69" s="22">
         <v>62.3</v>
@@ -28762,10 +28778,10 @@
     </row>
     <row r="70" spans="1:40">
       <c r="A70" s="25" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C70" s="22">
         <v>74.599999999999994</v>
@@ -28828,10 +28844,10 @@
     </row>
     <row r="71" spans="1:40">
       <c r="A71" s="25" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C71" s="22">
         <v>79.2</v>
@@ -28894,10 +28910,10 @@
     </row>
     <row r="72" spans="1:40">
       <c r="A72" s="25" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C72" s="22">
         <v>74.7</v>
@@ -28960,10 +28976,10 @@
     </row>
     <row r="73" spans="1:40">
       <c r="A73" s="25" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C73" s="22">
         <v>73.2</v>
@@ -29026,10 +29042,10 @@
     </row>
     <row r="74" spans="1:40">
       <c r="A74" s="25" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C74" s="22">
         <v>78</v>
@@ -29092,10 +29108,10 @@
     </row>
     <row r="75" spans="1:40">
       <c r="A75" s="25" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C75" s="22">
         <v>75.5</v>
@@ -29158,10 +29174,10 @@
     </row>
     <row r="76" spans="1:40">
       <c r="A76" s="25" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C76" s="22">
         <v>75.5</v>
@@ -29224,10 +29240,10 @@
     </row>
     <row r="77" spans="1:40">
       <c r="A77" s="25" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C77" s="22">
         <v>57.2</v>
@@ -29290,10 +29306,10 @@
     </row>
     <row r="78" spans="1:40">
       <c r="A78" s="25" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C78" s="22">
         <v>78.900000000000006</v>
@@ -29356,10 +29372,10 @@
     </row>
     <row r="79" spans="1:40">
       <c r="A79" s="25" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C79" s="22">
         <v>75.7</v>
@@ -29422,10 +29438,10 @@
     </row>
     <row r="80" spans="1:40">
       <c r="A80" s="25" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C80" s="22">
         <v>69.599999999999994</v>
@@ -29488,10 +29504,10 @@
     </row>
     <row r="81" spans="1:40">
       <c r="A81" s="25" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C81" s="22">
         <v>75.7</v>
@@ -29554,10 +29570,10 @@
     </row>
     <row r="82" spans="1:40">
       <c r="A82" s="25" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C82" s="22">
         <v>75.2</v>
@@ -29620,10 +29636,10 @@
     </row>
     <row r="83" spans="1:40">
       <c r="A83" s="25" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C83" s="22">
         <v>72.3</v>
@@ -29686,10 +29702,10 @@
     </row>
     <row r="84" spans="1:40">
       <c r="A84" s="25" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C84" s="22">
         <v>59.4</v>
@@ -29752,10 +29768,10 @@
     </row>
     <row r="85" spans="1:40">
       <c r="A85" s="25" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C85" s="22">
         <v>74.2</v>
@@ -29818,10 +29834,10 @@
     </row>
     <row r="86" spans="1:40">
       <c r="A86" s="25" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C86" s="22">
         <v>57.7</v>
@@ -29884,10 +29900,10 @@
     </row>
     <row r="87" spans="1:40">
       <c r="A87" s="25" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C87" s="22">
         <v>69.099999999999994</v>
@@ -29950,10 +29966,10 @@
     </row>
     <row r="88" spans="1:40">
       <c r="A88" s="25" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C88" s="22">
         <v>73.099999999999994</v>
@@ -30016,10 +30032,10 @@
     </row>
     <row r="89" spans="1:40">
       <c r="A89" s="25" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C89" s="22">
         <v>35.700000000000003</v>
@@ -30082,10 +30098,10 @@
     </row>
     <row r="90" spans="1:40">
       <c r="A90" s="25" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C90" s="22">
         <v>77.2</v>
@@ -30147,10 +30163,10 @@
       <c r="AN90" s="17"/>
     </row>
     <row r="91" spans="1:40" ht="15" customHeight="1">
-      <c r="A91" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="B91" s="74"/>
+      <c r="A91" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B91" s="71"/>
       <c r="C91" s="32">
         <v>67.3</v>
       </c>
@@ -30210,10 +30226,10 @@
       </c>
     </row>
     <row r="92" spans="1:40">
-      <c r="A92" s="74" t="s">
-        <v>17</v>
-      </c>
-      <c r="B92" s="74"/>
+      <c r="A92" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="71"/>
       <c r="C92" s="32"/>
       <c r="D92" s="34"/>
       <c r="E92" s="34"/>
@@ -30330,18 +30346,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="43.05" hidden="1" customHeight="1">
-      <c r="A1" s="96" t="s">
-        <v>271</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
+      <c r="A1" s="94" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
@@ -30353,91 +30369,91 @@
     </row>
     <row r="2" spans="1:18" ht="34.799999999999997">
       <c r="A2" s="7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="97"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="87">
+      <c r="B3" s="87"/>
+      <c r="C3" s="91">
         <v>1</v>
       </c>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87">
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91">
         <v>2</v>
       </c>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87">
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91">
         <v>3</v>
       </c>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87">
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91">
         <v>4</v>
       </c>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="87"/>
+      <c r="P3" s="91"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="91"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="87">
+      <c r="A4" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="87"/>
+      <c r="C4" s="91">
         <v>1.4</v>
       </c>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87">
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91">
         <v>3.2</v>
       </c>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87">
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91">
         <v>4.2</v>
       </c>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87">
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91">
         <v>5.0999999999999996</v>
       </c>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="91"/>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="83"/>
+      <c r="A5" s="87" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="87"/>
       <c r="C5" s="8">
         <v>0.2</v>
       </c>
@@ -30492,63 +30508,63 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="12" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C7" s="14">
         <v>0.69330000000000003</v>
@@ -30601,10 +30617,10 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C8" s="14">
         <v>0.70809999999999995</v>
@@ -30657,10 +30673,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="12" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C9" s="14">
         <v>0.39810000000000001</v>
@@ -30713,10 +30729,10 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="12" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C10" s="14">
         <v>0.82050000000000001</v>
@@ -30769,10 +30785,10 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="12" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C11" s="14">
         <v>0.73860000000000003</v>
@@ -30825,10 +30841,10 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="12" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C12" s="14">
         <v>0.22950000000000001</v>
@@ -30881,10 +30897,10 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="12" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C13" s="14">
         <v>0.80759999999999998</v>
@@ -30937,10 +30953,10 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="12" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C14" s="14">
         <v>0.77139999999999997</v>
@@ -30993,10 +31009,10 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="12" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C15" s="14">
         <v>0.66669999999999996</v>
@@ -31049,10 +31065,10 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C16" s="14">
         <v>0.73619999999999997</v>
@@ -31105,10 +31121,10 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="12" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C17" s="14">
         <v>0.68379999999999996</v>
@@ -31161,10 +31177,10 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="12" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C18" s="14">
         <v>0.75139999999999996</v>
@@ -31217,10 +31233,10 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="12" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C19" s="14">
         <v>0.54139999999999999</v>
@@ -31273,10 +31289,10 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="12" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C20" s="14">
         <v>0.46710000000000002</v>
@@ -31329,10 +31345,10 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="12" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C21" s="14">
         <v>0.73</v>
@@ -31385,10 +31401,10 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="12" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C22" s="14">
         <v>0.57709999999999995</v>
@@ -31441,10 +31457,10 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="12" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C23" s="14">
         <v>0.63429999999999997</v>
@@ -31497,10 +31513,10 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="12" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C24" s="14">
         <v>0.66759999999999997</v>
@@ -31553,10 +31569,10 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="12" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C25" s="14">
         <v>0.39950000000000002</v>
@@ -31609,10 +31625,10 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="12" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C26" s="14">
         <v>0.57189999999999996</v>
@@ -31665,10 +31681,10 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="12" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C27" s="14">
         <v>0.39810000000000001</v>
@@ -31721,10 +31737,10 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="12" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C28" s="14">
         <v>0.74519999999999997</v>
@@ -31777,10 +31793,10 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="12" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C29" s="14">
         <v>0.59760000000000002</v>
@@ -31833,10 +31849,10 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="12" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C30" s="14">
         <v>0.64949999999999997</v>
@@ -31889,10 +31905,10 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="12" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C31" s="14">
         <v>0.73899999999999999</v>
@@ -31945,10 +31961,10 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C32" s="14">
         <v>0.74139999999999995</v>
@@ -32001,10 +32017,10 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="12" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C33" s="14">
         <v>0.61899999999999999</v>
@@ -32057,10 +32073,10 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="12" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C34" s="14">
         <v>0.66949999999999998</v>
@@ -32113,10 +32129,10 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="12" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C35" s="14">
         <v>0.65139999999999998</v>
@@ -32169,10 +32185,10 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="12" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C36" s="14">
         <v>0.72140000000000004</v>
@@ -32225,10 +32241,10 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="12" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C37" s="14">
         <v>0.74860000000000004</v>
@@ -32281,10 +32297,10 @@
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="12" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C38" s="14">
         <v>0.67620000000000002</v>
@@ -32337,10 +32353,10 @@
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="12" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C39" s="14">
         <v>0.64480000000000004</v>
@@ -32393,10 +32409,10 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="12" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C40" s="14">
         <v>0.6462</v>
@@ -32449,10 +32465,10 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="12" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C41" s="14">
         <v>0.69620000000000004</v>
@@ -32505,10 +32521,10 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="12" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C42" s="14">
         <v>0.69430000000000003</v>
@@ -32561,10 +32577,10 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="12" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C43" s="14">
         <v>0.67620000000000002</v>
@@ -32617,10 +32633,10 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="12" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C44" s="14">
         <v>0.74809999999999999</v>
@@ -32673,10 +32689,10 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="12" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C45" s="14">
         <v>0.69099999999999995</v>
@@ -32729,10 +32745,10 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="12" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C46" s="14">
         <v>0.70289999999999997</v>
@@ -32785,10 +32801,10 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="12" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C47" s="14">
         <v>0.79759999999999998</v>
@@ -32841,10 +32857,10 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="12" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C48" s="14">
         <v>0.6976</v>
@@ -32897,10 +32913,10 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C49" s="14">
         <v>0.76859999999999995</v>
@@ -32953,10 +32969,10 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="12" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C50" s="14">
         <v>0.61099999999999999</v>
@@ -33009,10 +33025,10 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="12" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C51" s="14">
         <v>0.63100000000000001</v>
@@ -33065,10 +33081,10 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="12" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C52" s="14">
         <v>0.72670000000000001</v>
@@ -33121,10 +33137,10 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="12" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C53" s="14">
         <v>0.74139999999999995</v>
@@ -33177,10 +33193,10 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="12" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C54" s="14">
         <v>0.74860000000000004</v>
@@ -33233,10 +33249,10 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="12" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C55" s="14">
         <v>0.70809999999999995</v>
@@ -33289,10 +33305,10 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="12" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C56" s="14">
         <v>0.52949999999999997</v>
@@ -33345,10 +33361,10 @@
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="12" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C57" s="14">
         <v>0.61619999999999997</v>
@@ -33401,10 +33417,10 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="12" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C58" s="14">
         <v>0.71050000000000002</v>
@@ -33457,10 +33473,10 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="12" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C59" s="14">
         <v>0.62809999999999999</v>
@@ -33513,10 +33529,10 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="12" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C60" s="14">
         <v>0.65480000000000005</v>
@@ -33569,10 +33585,10 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="12" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C61" s="14">
         <v>0.68289999999999995</v>
@@ -33625,10 +33641,10 @@
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="12" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C62" s="14">
         <v>0.74139999999999995</v>
@@ -33681,10 +33697,10 @@
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="12" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C63" s="14">
         <v>0.76670000000000005</v>
@@ -33737,10 +33753,10 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="12" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C64" s="14">
         <v>0.56000000000000005</v>
@@ -33793,10 +33809,10 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" s="12" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C65" s="14">
         <v>0.7319</v>
@@ -33849,10 +33865,10 @@
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="12" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C66" s="14">
         <v>0.61619999999999997</v>
@@ -33905,10 +33921,10 @@
     </row>
     <row r="67" spans="1:18">
       <c r="A67" s="12" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C67" s="14">
         <v>0.58430000000000004</v>
@@ -33961,10 +33977,10 @@
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="12" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C68" s="14">
         <v>0.65139999999999998</v>
@@ -34017,10 +34033,10 @@
     </row>
     <row r="69" spans="1:18">
       <c r="A69" s="12" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C69" s="14">
         <v>0.78290000000000004</v>
@@ -34073,10 +34089,10 @@
     </row>
     <row r="70" spans="1:18">
       <c r="A70" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C70" s="14">
         <v>0.62290000000000001</v>
@@ -34129,10 +34145,10 @@
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="12" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C71" s="14">
         <v>0.74619999999999997</v>
@@ -34185,10 +34201,10 @@
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="12" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C72" s="14">
         <v>0.79190000000000005</v>
@@ -34241,10 +34257,10 @@
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="12" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C73" s="14">
         <v>0.74670000000000003</v>
@@ -34297,10 +34313,10 @@
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="12" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C74" s="14">
         <v>0.7319</v>
@@ -34353,10 +34369,10 @@
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="12" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C75" s="14">
         <v>0.78</v>
@@ -34409,10 +34425,10 @@
     </row>
     <row r="76" spans="1:18">
       <c r="A76" s="12" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C76" s="14">
         <v>0.75519999999999998</v>
@@ -34465,10 +34481,10 @@
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="12" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C77" s="14">
         <v>0.75519999999999998</v>
@@ -34521,10 +34537,10 @@
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="12" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C78" s="14">
         <v>0.57189999999999996</v>
@@ -34577,10 +34593,10 @@
     </row>
     <row r="79" spans="1:18">
       <c r="A79" s="12" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C79" s="14">
         <v>0.78859999999999997</v>
@@ -34633,10 +34649,10 @@
     </row>
     <row r="80" spans="1:18">
       <c r="A80" s="12" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C80" s="14">
         <v>0.7571</v>
@@ -34689,10 +34705,10 @@
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="12" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C81" s="14">
         <v>0.69620000000000004</v>
@@ -34745,10 +34761,10 @@
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="12" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C82" s="14">
         <v>0.7571</v>
@@ -34801,10 +34817,10 @@
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="12" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C83" s="14">
         <v>0.75239999999999996</v>
@@ -34857,10 +34873,10 @@
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="12" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C84" s="14">
         <v>0.72330000000000005</v>
@@ -34913,10 +34929,10 @@
     </row>
     <row r="85" spans="1:18">
       <c r="A85" s="12" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C85" s="14">
         <v>0.59430000000000005</v>
@@ -34969,10 +34985,10 @@
     </row>
     <row r="86" spans="1:18">
       <c r="A86" s="12" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C86" s="14">
         <v>0.7419</v>
@@ -35025,10 +35041,10 @@
     </row>
     <row r="87" spans="1:18">
       <c r="A87" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C87" s="14">
         <v>0.57669999999999999</v>
@@ -35081,10 +35097,10 @@
     </row>
     <row r="88" spans="1:18">
       <c r="A88" s="12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C88" s="14">
         <v>0.69140000000000001</v>
@@ -35137,10 +35153,10 @@
     </row>
     <row r="89" spans="1:18">
       <c r="A89" s="12" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C89" s="14">
         <v>0.73140000000000005</v>
@@ -35193,10 +35209,10 @@
     </row>
     <row r="90" spans="1:18">
       <c r="A90" s="12" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C90" s="14">
         <v>0.35709999999999997</v>
@@ -35249,10 +35265,10 @@
     </row>
     <row r="91" spans="1:18">
       <c r="A91" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C91" s="14">
         <v>0.77190000000000003</v>
@@ -35304,10 +35320,10 @@
       </c>
     </row>
     <row r="92" spans="1:18">
-      <c r="A92" s="93" t="s">
-        <v>16</v>
-      </c>
-      <c r="B92" s="94"/>
+      <c r="A92" s="99" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92" s="100"/>
       <c r="C92" s="15">
         <v>0.67269999999999996</v>
       </c>
@@ -35358,37 +35374,49 @@
       </c>
     </row>
     <row r="93" spans="1:18">
-      <c r="A93" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B93" s="94"/>
-      <c r="C93" s="95">
+      <c r="A93" s="99" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="100"/>
+      <c r="C93" s="101">
         <v>0.79769999999999996</v>
       </c>
-      <c r="D93" s="95"/>
-      <c r="E93" s="95"/>
-      <c r="F93" s="95"/>
-      <c r="G93" s="90">
+      <c r="D93" s="101"/>
+      <c r="E93" s="101"/>
+      <c r="F93" s="101"/>
+      <c r="G93" s="96">
         <v>0.79059999999999997</v>
       </c>
-      <c r="H93" s="91"/>
-      <c r="I93" s="91"/>
-      <c r="J93" s="92"/>
-      <c r="K93" s="90">
+      <c r="H93" s="97"/>
+      <c r="I93" s="97"/>
+      <c r="J93" s="98"/>
+      <c r="K93" s="96">
         <v>0.6754</v>
       </c>
-      <c r="L93" s="91"/>
-      <c r="M93" s="91"/>
-      <c r="N93" s="92"/>
-      <c r="O93" s="90">
+      <c r="L93" s="97"/>
+      <c r="M93" s="97"/>
+      <c r="N93" s="98"/>
+      <c r="O93" s="96">
         <v>0.82250000000000001</v>
       </c>
-      <c r="P93" s="91"/>
-      <c r="Q93" s="91"/>
-      <c r="R93" s="92"/>
+      <c r="P93" s="97"/>
+      <c r="Q93" s="97"/>
+      <c r="R93" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="K93:N93"/>
+    <mergeCell ref="O93:R93"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="G93:J93"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="O4:R4"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="C2:R2"/>
     <mergeCell ref="A3:B3"/>
@@ -35396,18 +35424,6 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="O3:R3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="K93:N93"/>
-    <mergeCell ref="O93:R93"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:F93"/>
-    <mergeCell ref="G93:J93"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
@@ -35437,114 +35453,114 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="67.05" customHeight="1">
-      <c r="A2" s="101" t="s">
-        <v>272</v>
-      </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
+      <c r="A2" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="66"/>
+      <c r="C3" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="J3" s="64"/>
+    </row>
+    <row r="4" spans="1:10" ht="25.95" customHeight="1">
+      <c r="A4" s="66"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="64" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1">
+      <c r="A7" s="66"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+    </row>
+    <row r="8" spans="1:10" ht="14.4">
+      <c r="A8" s="66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="64">
+        <v>0.15</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="98" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="98"/>
-    </row>
-    <row r="4" spans="1:10" ht="25.95" customHeight="1">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="98" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="98" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="98" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="98" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="98" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="98" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="98" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98" t="s">
-        <v>78</v>
-      </c>
-      <c r="J5" s="98" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="99"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1">
-      <c r="A7" s="99"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-    </row>
-    <row r="8" spans="1:10" ht="14.4">
-      <c r="A8" s="99" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="98">
-        <v>0.15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="D8" s="4">
         <v>15</v>
@@ -35558,21 +35574,21 @@
       <c r="G8" s="4">
         <v>0.2</v>
       </c>
-      <c r="H8" s="100">
+      <c r="H8" s="65">
         <v>0.79769999999999996</v>
       </c>
-      <c r="I8" s="98" t="s">
-        <v>273</v>
-      </c>
-      <c r="J8" s="100">
+      <c r="I8" s="64" t="s">
+        <v>263</v>
+      </c>
+      <c r="J8" s="65">
         <v>0.79769999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="14.4">
-      <c r="A9" s="99"/>
-      <c r="B9" s="98"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="64"/>
       <c r="C9" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D9" s="4">
         <v>15</v>
@@ -35586,15 +35602,15 @@
       <c r="G9" s="4">
         <v>0.3</v>
       </c>
-      <c r="H9" s="100"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="100"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="65"/>
     </row>
     <row r="10" spans="1:10" ht="14.4">
-      <c r="A10" s="99"/>
-      <c r="B10" s="98"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="64"/>
       <c r="C10" s="4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D10" s="4">
         <v>15</v>
@@ -35608,19 +35624,19 @@
       <c r="G10" s="4">
         <v>0.5</v>
       </c>
-      <c r="H10" s="100"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="100"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="65"/>
     </row>
     <row r="11" spans="1:10" ht="14.4">
-      <c r="A11" s="99" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="98">
+      <c r="A11" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="64">
         <v>0.25</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D11" s="4">
         <v>25</v>
@@ -35634,21 +35650,21 @@
       <c r="G11" s="4">
         <v>0.2</v>
       </c>
-      <c r="H11" s="100">
+      <c r="H11" s="65">
         <v>0.79059999999999997</v>
       </c>
-      <c r="I11" s="98" t="s">
-        <v>274</v>
-      </c>
-      <c r="J11" s="100">
+      <c r="I11" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="J11" s="65">
         <v>0.79059999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="14.4">
-      <c r="A12" s="99"/>
-      <c r="B12" s="98"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="64"/>
       <c r="C12" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D12" s="4">
         <v>25</v>
@@ -35662,15 +35678,15 @@
       <c r="G12" s="4">
         <v>0.3</v>
       </c>
-      <c r="H12" s="100"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="100"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:10" ht="13.95" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="98"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="64"/>
       <c r="C13" s="4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D13" s="4">
         <v>25</v>
@@ -35684,19 +35700,19 @@
       <c r="G13" s="4">
         <v>0.5</v>
       </c>
-      <c r="H13" s="100"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="100"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="1:10" ht="13.95" customHeight="1">
-      <c r="A14" s="99" t="s">
-        <v>275</v>
-      </c>
-      <c r="B14" s="98">
+      <c r="A14" s="66" t="s">
+        <v>265</v>
+      </c>
+      <c r="B14" s="64">
         <v>0.3</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D14" s="4">
         <v>30</v>
@@ -35710,21 +35726,21 @@
       <c r="G14" s="4">
         <v>0.2</v>
       </c>
-      <c r="H14" s="100">
+      <c r="H14" s="65">
         <v>0.6754</v>
       </c>
-      <c r="I14" s="98" t="s">
-        <v>276</v>
-      </c>
-      <c r="J14" s="100">
+      <c r="I14" s="64" t="s">
+        <v>266</v>
+      </c>
+      <c r="J14" s="65">
         <v>0.6754</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.95" customHeight="1">
-      <c r="A15" s="99"/>
-      <c r="B15" s="98"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="64"/>
       <c r="C15" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" s="4">
         <v>30</v>
@@ -35738,15 +35754,15 @@
       <c r="G15" s="4">
         <v>0.3</v>
       </c>
-      <c r="H15" s="100"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="100"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="65"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A16" s="99"/>
-      <c r="B16" s="98"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="64"/>
       <c r="C16" s="4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D16" s="4">
         <v>30</v>
@@ -35760,19 +35776,19 @@
       <c r="G16" s="4">
         <v>0.5</v>
       </c>
-      <c r="H16" s="100"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="100"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="65"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A17" s="99" t="s">
-        <v>277</v>
-      </c>
-      <c r="B17" s="98">
+      <c r="A17" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="B17" s="64">
         <v>0.3</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D17" s="4">
         <v>30</v>
@@ -35786,21 +35802,21 @@
       <c r="G17" s="4">
         <v>0.2</v>
       </c>
-      <c r="H17" s="100">
+      <c r="H17" s="65">
         <v>0.82250000000000001</v>
       </c>
-      <c r="I17" s="98" t="s">
-        <v>278</v>
-      </c>
-      <c r="J17" s="100">
+      <c r="I17" s="64" t="s">
+        <v>268</v>
+      </c>
+      <c r="J17" s="65">
         <v>0.82250000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="98"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="64"/>
       <c r="C18" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D18" s="4">
         <v>30</v>
@@ -35814,15 +35830,15 @@
       <c r="G18" s="4">
         <v>0.3</v>
       </c>
-      <c r="H18" s="100"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="100"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="65"/>
     </row>
     <row r="19" spans="1:10" ht="14.4">
-      <c r="A19" s="99"/>
-      <c r="B19" s="98"/>
+      <c r="A19" s="66"/>
+      <c r="B19" s="64"/>
       <c r="C19" s="4" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D19" s="4">
         <v>30</v>
@@ -35836,34 +35852,54 @@
       <c r="G19" s="4">
         <v>0.5</v>
       </c>
-      <c r="H19" s="100"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="100"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="65"/>
     </row>
     <row r="20" spans="1:10" ht="28.8">
       <c r="A20" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="98">
+        <v>74</v>
+      </c>
+      <c r="B20" s="64">
         <v>0.6</v>
       </c>
-      <c r="C20" s="98" t="s">
-        <v>279</v>
-      </c>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
+      <c r="C20" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
       <c r="F20" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" s="100">
+        <v>75</v>
+      </c>
+      <c r="G20" s="65">
         <v>0.76670000000000005</v>
       </c>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C3:G4"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="H11:H13"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="G20:J20"/>
@@ -35880,26 +35916,6 @@
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="H3:H7"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C3:G4"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36348,7 +36364,7 @@
   <sheetData>
     <row r="7" spans="2:3">
       <c r="B7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C7" s="2">
         <v>0.79769999999999996</v>
@@ -36356,7 +36372,7 @@
     </row>
     <row r="8" spans="2:3">
       <c r="B8" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2">
         <v>0.79059999999999997</v>
@@ -36364,7 +36380,7 @@
     </row>
     <row r="9" spans="2:3">
       <c r="B9" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C9" s="2">
         <v>0.6754</v>
@@ -36372,7 +36388,7 @@
     </row>
     <row r="10" spans="2:3">
       <c r="B10" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C10" s="2">
         <v>0.82250000000000001</v>
